--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134262241</v>
       </c>
       <c r="B2" t="n">
-        <v>99085</v>
+        <v>99086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134262241</v>
       </c>
       <c r="B2" t="n">
-        <v>99087</v>
+        <v>99094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134262241</v>
+        <v>118782353</v>
       </c>
       <c r="B2" t="n">
-        <v>99094</v>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,20 +703,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallmora, Kallmora, Dlr</t>
+          <t>Kallmora, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488605</v>
+        <v>488607</v>
       </c>
       <c r="R2" t="n">
-        <v>6782738</v>
+        <v>6782751</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ny lokal i vägkanten. Har aldrig vuxit där tidigare enligt närboende som idag är 85 år</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -775,10 +783,670 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126200060</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99024</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>504</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kallmora, Kallmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>488610</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6782755</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En meter från vägen på två ställen. Totalt 20 blommor</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134262231</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>504</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kallmora, Kallmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>488609</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6782755</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134262241</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>504</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kallmora, Kallmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>488605</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6782738</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134262466</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>504</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kallmora, Kallmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>488587</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6782735</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134262299</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kallmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488607</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6782751</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118782362</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101794</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222929</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Backruta</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Thalictrum simplex</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kallmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488607</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6782751</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134262299</v>
+        <v>135461686</v>
       </c>
       <c r="B7" t="n">
-        <v>99219</v>
+        <v>99101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,46 +1243,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kallmora, Dlr</t>
+          <t>Kallmora, Kallmora, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488607</v>
+        <v>488673</v>
       </c>
       <c r="R7" t="n">
-        <v>6782751</v>
+        <v>6782844</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,22 +1306,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,46 +1341,51 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118782362</v>
+        <v>134262299</v>
       </c>
       <c r="B8" t="n">
-        <v>101794</v>
+        <v>99219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222929</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backruta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thalictrum simplex</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallmora, Dlr</t>
@@ -1417,12 +1422,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,7 +1446,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1443,10 +1457,112 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118782362</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101794</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222929</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Backruta</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thalictrum simplex</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kallmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488607</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6782751</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Bengt Oldhammer</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118782353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126200060</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262231</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262241</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262466</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135461686</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262299</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,8 +1603,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118782362</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>135461686</v>
       </c>
       <c r="B7" t="n">
-        <v>99101</v>
+        <v>99148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>135461686</v>
       </c>
       <c r="B7" t="n">
-        <v>99148</v>
+        <v>99175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134262299</v>
+        <v>135461686</v>
       </c>
       <c r="B7" t="n">
-        <v>99219</v>
+        <v>99180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,46 +1273,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kallmora, Dlr</t>
+          <t>Kallmora, Kallmora, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488607</v>
+        <v>488673</v>
       </c>
       <c r="R7" t="n">
-        <v>6782751</v>
+        <v>6782844</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,22 +1336,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,51 +1371,56 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134262299</t>
+          <t>https://artportalen.se/Sighting/135461686</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118782362</v>
+        <v>134262299</v>
       </c>
       <c r="B8" t="n">
-        <v>101794</v>
+        <v>99219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222929</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backruta</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thalictrum simplex</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallmora, Dlr</t>
@@ -1452,12 +1457,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,7 +1481,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1478,11 +1492,118 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262299</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118782362</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101794</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222929</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Backruta</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thalictrum simplex</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kallmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488607</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6782751</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118782362</t>
         </is>
@@ -1497,6 +1618,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>135461686</v>
       </c>
       <c r="B7" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56344-2025 artfynd.xlsx
+++ b/artfynd/A 56344-2025 artfynd.xlsx
@@ -1265,7 +1265,7 @@
         <v>135461686</v>
       </c>
       <c r="B7" t="n">
-        <v>99182</v>
+        <v>99199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
